--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e861be9d7bbfc9a/Desktop/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E65F7D8-5239-4D81-9A6A-8D0158AA931D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176ACEF7-5515-4919-902D-80AA83F2D48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2346,7 +2346,7 @@
         <v>300</v>
       </c>
       <c r="C34" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D34" s="14">
         <v>60</v>
@@ -2365,11 +2365,11 @@
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>915</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>55</v>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{176ACEF7-5515-4919-902D-80AA83F2D48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EB0175-F995-4F8A-BEC3-D35F902F44C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>Aditya Kumar</t>
+  </si>
+  <si>
+    <t>day was very good</t>
   </si>
 </sst>
 </file>
@@ -2346,7 +2349,7 @@
         <v>300</v>
       </c>
       <c r="C34" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D34" s="14">
         <v>60</v>
@@ -2365,11 +2368,11 @@
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>915</v>
+        <v>920</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>55</v>
@@ -2385,26 +2388,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B35" s="14">
+        <v>340</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>50</v>
+      </c>
+      <c r="F35" s="14">
+        <v>150</v>
+      </c>
+      <c r="G35" s="14">
+        <v>3</v>
+      </c>
+      <c r="H35" s="14">
+        <v>200</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>880</v>
+      </c>
+      <c r="J35" s="15">
+        <f>IF(I35="","",1440-I35)</f>
+        <v>560</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EB0175-F995-4F8A-BEC3-D35F902F44C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E949C63-50F8-4C4B-A11A-CDB04BE256A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2434,26 +2434,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B36" s="14">
+        <v>320</v>
+      </c>
+      <c r="C36" s="14">
+        <v>50</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>70</v>
+      </c>
+      <c r="F36" s="14">
+        <v>250</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>150</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>960</v>
+      </c>
+      <c r="J36" s="15">
+        <f>IF(I36="","",1440-I36)</f>
+        <v>480</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E949C63-50F8-4C4B-A11A-CDB04BE256A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CD27CF-E112-4E4F-B33D-02A61A8F6BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>day was very good</t>
+  </si>
+  <si>
+    <t>day waas amazing</t>
   </si>
 </sst>
 </file>
@@ -2480,26 +2483,48 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
+      <c r="A37" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B37" s="14">
+        <v>300</v>
+      </c>
+      <c r="C37" s="14">
+        <v>20</v>
+      </c>
+      <c r="D37" s="14">
+        <v>200</v>
+      </c>
+      <c r="E37" s="14">
+        <v>150</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>135</v>
+      </c>
+      <c r="I37" s="15">
+        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <v>805</v>
+      </c>
+      <c r="J37" s="15">
+        <f>IF(I37="","",1440-I37)</f>
+        <v>635</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+      <c r="M37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CD27CF-E112-4E4F-B33D-02A61A8F6BD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1130155D-331D-4283-9EA7-55B2E8CA2A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>day waas amazing</t>
+  </si>
+  <si>
+    <t>day w as crazy</t>
   </si>
 </sst>
 </file>
@@ -2518,7 +2521,9 @@
       <c r="K37" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L37" s="16"/>
+      <c r="L37" s="16" t="s">
+        <v>61</v>
+      </c>
       <c r="M37" s="16" t="s">
         <v>56</v>
       </c>
@@ -2527,26 +2532,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B38" s="14">
+        <v>330</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>180</v>
+      </c>
+      <c r="E38" s="14">
+        <v>100</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>250</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>890</v>
+      </c>
+      <c r="J38" s="15">
+        <f>IF(I38="","",1440-I38)</f>
+        <v>550</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1130155D-331D-4283-9EA7-55B2E8CA2A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C452D7-C8CC-414F-8DE9-77BD6E44B8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>day w as crazy</t>
+  </si>
+  <si>
+    <t>day was so so</t>
   </si>
 </sst>
 </file>
@@ -2578,26 +2581,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B39" s="14">
+        <v>240</v>
+      </c>
+      <c r="C39" s="14">
+        <v>20</v>
+      </c>
+      <c r="D39" s="14">
+        <v>150</v>
+      </c>
+      <c r="E39" s="14">
+        <v>150</v>
+      </c>
+      <c r="F39" s="14">
+        <v>4</v>
+      </c>
+      <c r="G39" s="14">
+        <v>200</v>
+      </c>
+      <c r="H39" s="14">
+        <v>100</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>664</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>776</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C452D7-C8CC-414F-8DE9-77BD6E44B8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A31C46-14B9-4EB3-B719-FC86321F3CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>day was so so</t>
+  </si>
+  <si>
+    <t>day was very busy</t>
   </si>
 </sst>
 </file>
@@ -2627,26 +2630,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B40" s="14">
+        <v>200</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>120</v>
+      </c>
+      <c r="F40" s="14">
+        <v>7</v>
+      </c>
+      <c r="G40" s="14">
+        <v>350</v>
+      </c>
+      <c r="H40" s="14">
+        <v>98</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>575</v>
+      </c>
+      <c r="J40" s="15">
+        <f>IF(I40="","",1440-I40)</f>
+        <v>865</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A31C46-14B9-4EB3-B719-FC86321F3CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480789F6-8D67-4FB1-8E84-B15C7F57E9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>day was very busy</t>
+  </si>
+  <si>
+    <t>day wasdecent</t>
   </si>
 </sst>
 </file>
@@ -2600,21 +2603,21 @@
         <v>150</v>
       </c>
       <c r="F39" s="14">
+        <v>200</v>
+      </c>
+      <c r="G39" s="14">
         <v>4</v>
-      </c>
-      <c r="G39" s="14">
-        <v>200</v>
       </c>
       <c r="H39" s="14">
         <v>100</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>664</v>
+        <v>860</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>776</v>
+        <v>580</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>49</v>
@@ -2646,21 +2649,21 @@
         <v>120</v>
       </c>
       <c r="F40" s="14">
+        <v>350</v>
+      </c>
+      <c r="G40" s="14">
         <v>7</v>
-      </c>
-      <c r="G40" s="14">
-        <v>350</v>
       </c>
       <c r="H40" s="14">
         <v>98</v>
       </c>
       <c r="I40" s="15">
-        <f t="shared" si="0"/>
-        <v>575</v>
+        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <v>918</v>
       </c>
       <c r="J40" s="15">
         <f>IF(I40="","",1440-I40)</f>
-        <v>865</v>
+        <v>522</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>55</v>
@@ -2676,26 +2679,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B41" s="14">
+        <v>200</v>
+      </c>
+      <c r="C41" s="14">
+        <v>20</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>120</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>200</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>1010</v>
+      </c>
+      <c r="J41" s="15">
+        <f>IF(I41="","",1440-I41)</f>
+        <v>430</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{480789F6-8D67-4FB1-8E84-B15C7F57E9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3091FD9E-0A6D-4001-B78B-97B0279387CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -289,7 +289,7 @@
     <t>day was very busy</t>
   </si>
   <si>
-    <t>day wasdecent</t>
+    <t xml:space="preserve"> day was decent</t>
   </si>
 </sst>
 </file>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3091FD9E-0A6D-4001-B78B-97B0279387CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E512953-F40F-4D61-A6F7-A1C54C588A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t xml:space="preserve"> day was decent</t>
+  </si>
+  <si>
+    <t>day was good</t>
   </si>
 </sst>
 </file>
@@ -2725,26 +2728,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+      <c r="A42" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B42" s="14">
+        <v>210</v>
+      </c>
+      <c r="C42" s="14">
+        <v>10</v>
+      </c>
+      <c r="D42" s="14">
+        <v>110</v>
+      </c>
+      <c r="E42" s="14">
+        <v>109</v>
+      </c>
+      <c r="F42" s="14">
+        <v>100</v>
+      </c>
+      <c r="G42" s="14">
+        <v>2</v>
+      </c>
+      <c r="H42" s="14">
+        <v>250</v>
+      </c>
+      <c r="I42" s="15">
+        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <v>789</v>
+      </c>
+      <c r="J42" s="15">
+        <f>IF(I42="","",1440-I42)</f>
+        <v>651</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E512953-F40F-4D61-A6F7-A1C54C588A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830FCE5A-E624-4E5A-B43A-9B10B8E50A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830FCE5A-E624-4E5A-B43A-9B10B8E50A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763105C-3220-46D5-BCAA-AD6A4C0BECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2774,26 +2774,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+      <c r="A43" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B43" s="14">
+        <v>178</v>
+      </c>
+      <c r="C43" s="14">
+        <v>10</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>129</v>
+      </c>
+      <c r="F43" s="14">
+        <v>250</v>
+      </c>
+      <c r="G43" s="14">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14">
+        <v>246</v>
+      </c>
+      <c r="I43" s="15">
+        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <v>933</v>
+      </c>
+      <c r="J43" s="15">
+        <f>IF(I43="","",1440-I43)</f>
+        <v>507</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763105C-3220-46D5-BCAA-AD6A4C0BECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7E044D-5176-44EA-A0A6-C3755A0A7B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>day was good</t>
+  </si>
+  <si>
+    <t>day spent weel</t>
   </si>
 </sst>
 </file>
@@ -2820,26 +2823,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B44" s="14">
+        <v>235</v>
+      </c>
+      <c r="C44" s="14">
+        <v>10</v>
+      </c>
+      <c r="D44" s="14">
+        <v>170</v>
+      </c>
+      <c r="E44" s="14">
+        <v>150</v>
+      </c>
+      <c r="F44" s="14">
+        <v>100</v>
+      </c>
+      <c r="G44" s="14">
+        <v>2</v>
+      </c>
+      <c r="H44" s="14">
+        <v>300</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>965</v>
+      </c>
+      <c r="J44" s="15">
+        <f>IF(I44="","",1440-I44)</f>
+        <v>475</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12629170.xlsx
+++ b/12629170.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7E044D-5176-44EA-A0A6-C3755A0A7B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00765874-6477-4023-8315-EB0D907DBFF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>day spent weel</t>
+  </si>
+  <si>
+    <t>too hetect</t>
   </si>
 </sst>
 </file>
@@ -2869,26 +2872,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B45" s="14">
+        <v>200</v>
+      </c>
+      <c r="C45" s="14">
+        <v>18</v>
+      </c>
+      <c r="D45" s="14">
+        <v>210</v>
+      </c>
+      <c r="E45" s="14">
+        <v>100</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>70</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>598</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>842</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
